--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N15_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N15_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.06350495984661</v>
+        <v>8.297819555975074</v>
       </c>
       <c r="D2" t="n">
-        <v>50.07631266182793</v>
+        <v>8.13740080754704</v>
       </c>
       <c r="E2" t="n">
-        <v>14.42407737003665</v>
+        <v>2.343912572630956</v>
       </c>
       <c r="F2" t="n">
-        <v>14.78116075950465</v>
+        <v>2.401938623419507</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.27816183347547</v>
+        <v>8.820201297939763</v>
       </c>
       <c r="D3" t="n">
-        <v>53.24892352285912</v>
+        <v>8.652950072464607</v>
       </c>
       <c r="E3" t="n">
-        <v>14.42407737003665</v>
+        <v>2.343912572630956</v>
       </c>
       <c r="F3" t="n">
-        <v>14.78116075950465</v>
+        <v>2.401938623419507</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.65385000676229</v>
+        <v>8.556250626098873</v>
       </c>
       <c r="D4" t="n">
-        <v>52.1202122610312</v>
+        <v>8.469534492417569</v>
       </c>
       <c r="E4" t="n">
-        <v>14.42407737003665</v>
+        <v>2.343912572630956</v>
       </c>
       <c r="F4" t="n">
-        <v>14.78116075950465</v>
+        <v>2.401938623419507</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.15109516021671</v>
+        <v>7.499552963535215</v>
       </c>
       <c r="D5" t="n">
-        <v>45.25869613208545</v>
+        <v>7.354538121463887</v>
       </c>
       <c r="E5" t="n">
-        <v>14.42407737003665</v>
+        <v>2.343912572630956</v>
       </c>
       <c r="F5" t="n">
-        <v>14.78116075950465</v>
+        <v>2.401938623419507</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>46.59849340345475</v>
+        <v>7.572255178061397</v>
       </c>
       <c r="D6" t="n">
-        <v>45.84864531123191</v>
+        <v>7.450404863075186</v>
       </c>
       <c r="E6" t="n">
-        <v>14.42407737003665</v>
+        <v>2.343912572630956</v>
       </c>
       <c r="F6" t="n">
-        <v>14.78116075950465</v>
+        <v>2.401938623419507</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47.24908303579144</v>
+        <v>7.677975993316108</v>
       </c>
       <c r="D7" t="n">
-        <v>46.21361380941322</v>
+        <v>7.509712244029649</v>
       </c>
       <c r="E7" t="n">
-        <v>14.42407737003665</v>
+        <v>2.343912572630956</v>
       </c>
       <c r="F7" t="n">
-        <v>14.78116075950465</v>
+        <v>2.401938623419507</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.04516201366071</v>
+        <v>4.882338827219865</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37828410260382</v>
+        <v>4.773971166673122</v>
       </c>
       <c r="E8" t="n">
-        <v>14.42407737003665</v>
+        <v>2.343912572630956</v>
       </c>
       <c r="F8" t="n">
-        <v>14.78116075950465</v>
+        <v>2.401938623419507</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>24.71864826650673</v>
+        <v>4.016780343307344</v>
       </c>
       <c r="D9" t="n">
-        <v>23.75271743340776</v>
+        <v>3.859816582928762</v>
       </c>
       <c r="E9" t="n">
-        <v>14.42407737003665</v>
+        <v>2.343912572630956</v>
       </c>
       <c r="F9" t="n">
-        <v>14.78116075950465</v>
+        <v>2.401938623419507</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>14.00816385111059</v>
+        <v>2.276326625805471</v>
       </c>
       <c r="D10" t="n">
-        <v>12.98898143259212</v>
+        <v>2.11070948279622</v>
       </c>
       <c r="E10" t="n">
-        <v>14.42407737003665</v>
+        <v>2.343912572630956</v>
       </c>
       <c r="F10" t="n">
-        <v>14.78116075950465</v>
+        <v>2.401938623419507</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>51.92440340578274</v>
+        <v>8.437715553439695</v>
       </c>
       <c r="D11" t="n">
-        <v>52.43865263792147</v>
+        <v>8.521281053662239</v>
       </c>
       <c r="E11" t="n">
-        <v>14.42407737003665</v>
+        <v>2.343912572630956</v>
       </c>
       <c r="F11" t="n">
-        <v>14.78116075950465</v>
+        <v>2.401938623419507</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>63.84924242983501</v>
+        <v>10.37550189484819</v>
       </c>
       <c r="D12" t="n">
-        <v>64.48993949962181</v>
+        <v>10.47961516868854</v>
       </c>
       <c r="E12" t="n">
-        <v>14.42407737003665</v>
+        <v>2.343912572630956</v>
       </c>
       <c r="F12" t="n">
-        <v>14.78116075950465</v>
+        <v>2.401938623419507</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>67.46602062043151</v>
+        <v>10.96322835082012</v>
       </c>
       <c r="D13" t="n">
-        <v>68.17378709278307</v>
+        <v>11.07824040257725</v>
       </c>
       <c r="E13" t="n">
-        <v>14.42407737003665</v>
+        <v>2.343912572630956</v>
       </c>
       <c r="F13" t="n">
-        <v>14.78116075950465</v>
+        <v>2.401938623419507</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>25.1730413095226</v>
+        <v>4.090619212797422</v>
       </c>
       <c r="D14" t="n">
-        <v>26.16146679445432</v>
+        <v>4.251238354098827</v>
       </c>
       <c r="E14" t="n">
-        <v>14.42407737003665</v>
+        <v>2.343912572630956</v>
       </c>
       <c r="F14" t="n">
-        <v>14.78116075950465</v>
+        <v>2.401938623419507</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>53.41485424004028</v>
+        <v>8.679913814006545</v>
       </c>
       <c r="D15" t="n">
-        <v>54.31224729629789</v>
+        <v>8.825740185648408</v>
       </c>
       <c r="E15" t="n">
-        <v>14.42407737003665</v>
+        <v>2.343912572630956</v>
       </c>
       <c r="F15" t="n">
-        <v>14.78116075950465</v>
+        <v>2.401938623419507</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>68.23211833134938</v>
+        <v>11.08771922884427</v>
       </c>
       <c r="D16" t="n">
-        <v>69.13232940337735</v>
+        <v>11.23400352804882</v>
       </c>
       <c r="E16" t="n">
-        <v>14.42407737003665</v>
+        <v>2.343912572630956</v>
       </c>
       <c r="F16" t="n">
-        <v>14.78116075950465</v>
+        <v>2.401938623419507</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>37.71090799152911</v>
+        <v>6.128022548623481</v>
       </c>
       <c r="D17" t="n">
-        <v>38.74299900454104</v>
+        <v>6.295737338237919</v>
       </c>
       <c r="E17" t="n">
-        <v>14.42407737003665</v>
+        <v>2.343912572630956</v>
       </c>
       <c r="F17" t="n">
-        <v>14.78116075950465</v>
+        <v>2.401938623419507</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>39.21897704191296</v>
+        <v>6.373083769310857</v>
       </c>
       <c r="D18" t="n">
-        <v>39.76469129741957</v>
+        <v>6.461762335830681</v>
       </c>
       <c r="E18" t="n">
-        <v>14.42407737003665</v>
+        <v>2.343912572630956</v>
       </c>
       <c r="F18" t="n">
-        <v>14.78116075950465</v>
+        <v>2.401938623419507</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>59.98025362819938</v>
+        <v>9.7467912145824</v>
       </c>
       <c r="D19" t="n">
-        <v>60.98630838622334</v>
+        <v>9.910275112761294</v>
       </c>
       <c r="E19" t="n">
-        <v>14.42407737003665</v>
+        <v>2.343912572630956</v>
       </c>
       <c r="F19" t="n">
-        <v>14.78116075950465</v>
+        <v>2.401938623419507</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>47.09527845991084</v>
+        <v>7.652982749735513</v>
       </c>
       <c r="D20" t="n">
-        <v>47.98322388166125</v>
+        <v>7.797273880769954</v>
       </c>
       <c r="E20" t="n">
-        <v>14.42407737003665</v>
+        <v>2.343912572630956</v>
       </c>
       <c r="F20" t="n">
-        <v>14.78116075950465</v>
+        <v>2.401938623419507</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>60.25357699873067</v>
+        <v>9.791206262293734</v>
       </c>
       <c r="D21" t="n">
-        <v>61.28443587253343</v>
+        <v>9.958720829286683</v>
       </c>
       <c r="E21" t="n">
-        <v>14.42407737003665</v>
+        <v>2.343912572630956</v>
       </c>
       <c r="F21" t="n">
-        <v>14.78116075950465</v>
+        <v>2.401938623419507</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
